--- a/src/files/geOperarioGeneral.xlsx
+++ b/src/files/geOperarioGeneral.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\proyects\hallazgos\hallazgos-api\src\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FC82E7-B0C6-423F-9F04-B38BB35632B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1763A4AB-007B-4261-AEB0-51A548DB3D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -599,47 +599,107 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="1" applyFill="1" applyBorder="1"/>
@@ -660,25 +720,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -702,74 +750,26 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1236,67 +1236,67 @@
   <sheetData>
     <row r="1" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14"/>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="64" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="65"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="68"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="41"/>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="69" t="s">
+      <c r="B3" s="43"/>
+      <c r="C3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="70" t="s">
+      <c r="D3" s="43"/>
+      <c r="E3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="71"/>
-      <c r="G3" s="72" t="s">
+      <c r="F3" s="46"/>
+      <c r="G3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="72"/>
-      <c r="I3" s="73"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="48"/>
     </row>
     <row r="4" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="78"/>
-    </row>
-    <row r="5" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="79" t="s">
+      <c r="A4" s="49"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="54"/>
+    </row>
+    <row r="5" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="80"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
@@ -1312,271 +1312,271 @@
       <c r="G5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="82"/>
-    </row>
-    <row r="6" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46"/>
-      <c r="B6" s="47"/>
+      <c r="I5" s="58"/>
+    </row>
+    <row r="6" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67"/>
       <c r="C6" s="21"/>
       <c r="D6" s="11"/>
       <c r="E6" s="12"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="31"/>
-    </row>
-    <row r="7" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="37"/>
-      <c r="B7" s="38"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:9" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="25"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="21"/>
       <c r="D7" s="11"/>
       <c r="E7" s="12"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="31"/>
-    </row>
-    <row r="8" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="48"/>
-      <c r="B8" s="49"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+    </row>
+    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="21"/>
       <c r="D8" s="5"/>
       <c r="E8" s="20"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="33"/>
-    </row>
-    <row r="9" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="48"/>
-      <c r="B9" s="49"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="32"/>
+    </row>
+    <row r="9" spans="1:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="33"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="21"/>
       <c r="D9" s="5"/>
       <c r="E9" s="20"/>
       <c r="F9" s="1"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="33"/>
-    </row>
-    <row r="10" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="48"/>
-      <c r="B10" s="49"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="21"/>
       <c r="D10" s="5"/>
       <c r="E10" s="20"/>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="33"/>
-    </row>
-    <row r="11" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="83"/>
-      <c r="B11" s="84"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="32"/>
+    </row>
+    <row r="11" spans="1:9" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="21"/>
       <c r="D11" s="5"/>
       <c r="E11" s="20"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="33"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="48"/>
-      <c r="B12" s="49"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="21"/>
       <c r="D12" s="11"/>
       <c r="E12" s="12"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="31"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="28"/>
     </row>
     <row r="13" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="37"/>
-      <c r="B13" s="38"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="21"/>
       <c r="D13" s="11"/>
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="31"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="28"/>
     </row>
     <row r="14" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="21"/>
       <c r="D14" s="11"/>
       <c r="E14" s="12"/>
       <c r="F14" s="1"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="33"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="38"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="21"/>
       <c r="D15" s="11"/>
       <c r="E15" s="12"/>
       <c r="F15" s="1"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="33"/>
-    </row>
-    <row r="16" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="37"/>
-      <c r="B16" s="38"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="32"/>
+    </row>
+    <row r="16" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="21"/>
       <c r="D16" s="22"/>
       <c r="E16" s="12"/>
       <c r="F16" s="1"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="31"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="28"/>
     </row>
     <row r="17" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="38"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="21"/>
       <c r="D17" s="22"/>
       <c r="E17" s="12"/>
       <c r="F17" s="1"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="31"/>
-    </row>
-    <row r="18" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="37"/>
-      <c r="B18" s="38"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="28"/>
+    </row>
+    <row r="18" spans="1:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22"/>
       <c r="E18" s="12"/>
       <c r="F18" s="23"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="31"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="28"/>
     </row>
     <row r="19" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="21"/>
       <c r="D19" s="11"/>
       <c r="E19" s="12"/>
       <c r="F19" s="1"/>
       <c r="G19" s="24"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="31"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="28"/>
     </row>
     <row r="20" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="21"/>
       <c r="D20" s="11"/>
       <c r="E20" s="12"/>
       <c r="F20" s="1"/>
       <c r="G20" s="24"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="31"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="28"/>
     </row>
     <row r="21" spans="1:9" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="21"/>
       <c r="D21" s="11"/>
       <c r="E21" s="12"/>
       <c r="F21" s="1"/>
       <c r="G21" s="24"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="31"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="37"/>
-      <c r="B22" s="38"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="21"/>
       <c r="D22" s="11"/>
       <c r="E22" s="12"/>
       <c r="F22" s="1"/>
       <c r="G22" s="24"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="31"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="28"/>
     </row>
     <row r="23" spans="1:9" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="26"/>
       <c r="C23" s="21"/>
       <c r="D23" s="11"/>
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
       <c r="G23" s="24"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="31"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="28"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="36"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="84"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="57"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="73"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="60"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="76"/>
     </row>
     <row r="27" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="29"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="82"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="41"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="43"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="63"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
@@ -1586,16 +1586,16 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="50"/>
-      <c r="B30" s="51"/>
+      <c r="A30" s="68"/>
+      <c r="B30" s="69"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
       <c r="G30" s="6"/>
       <c r="H30" s="7"/>
       <c r="I30" s="16"/>
@@ -1606,16 +1606,16 @@
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="61" t="s">
+      <c r="D31" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="25" t="s">
+      <c r="H31" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="I31" s="26"/>
+      <c r="I31" s="79"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18"/>
@@ -1627,43 +1627,30 @@
       </c>
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="40"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="60"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="H29:I29"/>
@@ -1680,22 +1667,35 @@
     <mergeCell ref="F25:I25"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="D31:F31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="H21:I21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
@@ -1706,6 +1706,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F25040A21B6C0B4DAD6A4A01C7D738FF" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a942d2c141cf3d2f503a3772f082487d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a37af1ee-9152-44d4-b447-8af1d1bb59e8" xmlns:ns3="79cc9dd1-df6d-441a-a0b4-ff482f600b8c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="175775575e6489816cf62581b5bb7970" ns2:_="" ns3:_="">
     <xsd:import namespace="a37af1ee-9152-44d4-b447-8af1d1bb59e8"/>
@@ -1934,20 +1943,19 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75F0ADA-CCC4-4671-AD81-146B4A5EA00D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D40BD7-8535-49C9-9805-FFA2A2A7C7BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1966,14 +1974,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75F0ADA-CCC4-4671-AD81-146B4A5EA00D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32B8C814-F910-4046-8DF2-10F4284CB23A}">
   <ds:schemaRefs>
